--- a/database/event/6372/event_6372_evp_summary.xlsx
+++ b/database/event/6372/event_6372_evp_summary.xlsx
@@ -496,28 +496,28 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7.6028</v>
+        <v>8.2738</v>
       </c>
       <c r="C2" t="n">
-        <v>4.4028</v>
+        <v>4.7914</v>
       </c>
       <c r="D2" t="n">
-        <v>2.65</v>
+        <v>2.8524</v>
       </c>
       <c r="E2" t="n">
-        <v>7.6028</v>
+        <v>8.2738</v>
       </c>
       <c r="F2" t="n">
-        <v>2.5035</v>
+        <v>3.1745</v>
       </c>
       <c r="G2" t="n">
         <v>5.0993</v>
       </c>
       <c r="H2" t="n">
-        <v>2.5035</v>
+        <v>3.1745</v>
       </c>
       <c r="I2" t="n">
-        <v>2.5035</v>
+        <v>3.1745</v>
       </c>
       <c r="J2" t="n">
         <v>5.0993</v>
@@ -529,7 +529,7 @@
         <v>217</v>
       </c>
       <c r="M2" t="n">
-        <v>7.6028</v>
+        <v>8.273800000000001</v>
       </c>
       <c r="N2" t="n">
         <v>365</v>
@@ -538,81 +538,81 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>s1mple</t>
+          <t>Spinx</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.3607</v>
+        <v>5.5902</v>
       </c>
       <c r="C3" t="n">
-        <v>3.1044</v>
+        <v>3.2373</v>
       </c>
       <c r="D3" t="n">
-        <v>1.7442</v>
+        <v>1.7832</v>
       </c>
       <c r="E3" t="n">
-        <v>5.3607</v>
+        <v>5.5902</v>
       </c>
       <c r="F3" t="n">
-        <v>2.2895</v>
+        <v>4.0745</v>
       </c>
       <c r="G3" t="n">
-        <v>3.0711</v>
+        <v>1.5157</v>
       </c>
       <c r="H3" t="n">
-        <v>2.2895</v>
+        <v>4.0858</v>
       </c>
       <c r="I3" t="n">
-        <v>2.2895</v>
+        <v>4.0858</v>
       </c>
       <c r="J3" t="n">
-        <v>3.0711</v>
+        <v>1.5157</v>
       </c>
       <c r="K3" t="n">
-        <v>132</v>
+        <v>152</v>
       </c>
       <c r="L3" t="n">
-        <v>192</v>
+        <v>105</v>
       </c>
       <c r="M3" t="n">
-        <v>5.3606</v>
+        <v>5.6015</v>
       </c>
       <c r="N3" t="n">
-        <v>324</v>
+        <v>257</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>b1t</t>
+          <t>s1mple</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.6234</v>
+        <v>5.3607</v>
       </c>
       <c r="C4" t="n">
-        <v>2.6774</v>
+        <v>3.1044</v>
       </c>
       <c r="D4" t="n">
-        <v>1.4464</v>
+        <v>1.6918</v>
       </c>
       <c r="E4" t="n">
-        <v>4.6234</v>
+        <v>5.3607</v>
       </c>
       <c r="F4" t="n">
-        <v>3.3326</v>
+        <v>2.2895</v>
       </c>
       <c r="G4" t="n">
-        <v>1.2908</v>
+        <v>3.0711</v>
       </c>
       <c r="H4" t="n">
-        <v>3.3326</v>
+        <v>2.2895</v>
       </c>
       <c r="I4" t="n">
-        <v>3.3326</v>
+        <v>2.2895</v>
       </c>
       <c r="J4" t="n">
-        <v>1.2908</v>
+        <v>3.0711</v>
       </c>
       <c r="K4" t="n">
         <v>132</v>
@@ -621,7 +621,7 @@
         <v>192</v>
       </c>
       <c r="M4" t="n">
-        <v>4.6234</v>
+        <v>5.3606</v>
       </c>
       <c r="N4" t="n">
         <v>324</v>
@@ -630,81 +630,81 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Spinx</t>
+          <t>b1t</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.5414</v>
+        <v>5.1553</v>
       </c>
       <c r="C5" t="n">
-        <v>2.6299</v>
+        <v>2.9855</v>
       </c>
       <c r="D5" t="n">
-        <v>1.4133</v>
+        <v>1.61</v>
       </c>
       <c r="E5" t="n">
-        <v>4.5414</v>
+        <v>5.1553</v>
       </c>
       <c r="F5" t="n">
-        <v>3.0257</v>
+        <v>3.8645</v>
       </c>
       <c r="G5" t="n">
-        <v>1.5157</v>
+        <v>1.2908</v>
       </c>
       <c r="H5" t="n">
-        <v>3.0257</v>
+        <v>3.8645</v>
       </c>
       <c r="I5" t="n">
-        <v>3.0257</v>
+        <v>3.8645</v>
       </c>
       <c r="J5" t="n">
-        <v>1.5157</v>
+        <v>1.2908</v>
       </c>
       <c r="K5" t="n">
-        <v>152</v>
+        <v>132</v>
       </c>
       <c r="L5" t="n">
-        <v>105</v>
+        <v>192</v>
       </c>
       <c r="M5" t="n">
-        <v>4.5414</v>
+        <v>5.1553</v>
       </c>
       <c r="N5" t="n">
-        <v>257</v>
+        <v>324</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>broky</t>
+          <t>ropz</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.2187</v>
+        <v>4.438</v>
       </c>
       <c r="C6" t="n">
-        <v>2.4431</v>
+        <v>2.5701</v>
       </c>
       <c r="D6" t="n">
-        <v>1.2829</v>
+        <v>1.3242</v>
       </c>
       <c r="E6" t="n">
-        <v>4.2187</v>
+        <v>4.438</v>
       </c>
       <c r="F6" t="n">
-        <v>2.5404</v>
+        <v>2.3229</v>
       </c>
       <c r="G6" t="n">
-        <v>1.6783</v>
+        <v>2.1151</v>
       </c>
       <c r="H6" t="n">
-        <v>2.5404</v>
+        <v>2.3229</v>
       </c>
       <c r="I6" t="n">
-        <v>2.5404</v>
+        <v>2.3229</v>
       </c>
       <c r="J6" t="n">
-        <v>1.6783</v>
+        <v>2.1151</v>
       </c>
       <c r="K6" t="n">
         <v>148</v>
@@ -713,7 +713,7 @@
         <v>217</v>
       </c>
       <c r="M6" t="n">
-        <v>4.2187</v>
+        <v>4.438000000000001</v>
       </c>
       <c r="N6" t="n">
         <v>365</v>
@@ -722,35 +722,35 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ropz</t>
+          <t>broky</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.8915</v>
+        <v>4.2187</v>
       </c>
       <c r="C7" t="n">
-        <v>2.2536</v>
+        <v>2.4431</v>
       </c>
       <c r="D7" t="n">
-        <v>1.1507</v>
+        <v>1.2368</v>
       </c>
       <c r="E7" t="n">
-        <v>3.8915</v>
+        <v>4.2187</v>
       </c>
       <c r="F7" t="n">
-        <v>1.7764</v>
+        <v>2.5404</v>
       </c>
       <c r="G7" t="n">
-        <v>2.1151</v>
+        <v>1.6783</v>
       </c>
       <c r="H7" t="n">
-        <v>1.7764</v>
+        <v>2.5404</v>
       </c>
       <c r="I7" t="n">
-        <v>1.7764</v>
+        <v>2.5404</v>
       </c>
       <c r="J7" t="n">
-        <v>2.1151</v>
+        <v>1.6783</v>
       </c>
       <c r="K7" t="n">
         <v>148</v>
@@ -759,7 +759,7 @@
         <v>217</v>
       </c>
       <c r="M7" t="n">
-        <v>3.8915</v>
+        <v>4.2187</v>
       </c>
       <c r="N7" t="n">
         <v>365</v>
@@ -768,219 +768,219 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>stavn</t>
+          <t>dycha</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.8006</v>
+        <v>3.9988</v>
       </c>
       <c r="C8" t="n">
-        <v>2.2009</v>
+        <v>2.3157</v>
       </c>
       <c r="D8" t="n">
-        <v>1.114</v>
+        <v>1.1492</v>
       </c>
       <c r="E8" t="n">
-        <v>3.8006</v>
+        <v>3.9988</v>
       </c>
       <c r="F8" t="n">
-        <v>3.1586</v>
+        <v>3.7463</v>
       </c>
       <c r="G8" t="n">
-        <v>0.642</v>
+        <v>0.2525</v>
       </c>
       <c r="H8" t="n">
-        <v>3.1586</v>
+        <v>3.7463</v>
       </c>
       <c r="I8" t="n">
-        <v>3.1733</v>
+        <v>3.7463</v>
       </c>
       <c r="J8" t="n">
-        <v>0.642</v>
+        <v>0.2525</v>
       </c>
       <c r="K8" t="n">
-        <v>252</v>
+        <v>152</v>
       </c>
       <c r="L8" t="n">
-        <v>80</v>
+        <v>105</v>
       </c>
       <c r="M8" t="n">
-        <v>3.8153</v>
+        <v>3.9988</v>
       </c>
       <c r="N8" t="n">
-        <v>332</v>
+        <v>257</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>dycha</t>
+          <t>m0NESY</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.7385</v>
+        <v>3.9705</v>
       </c>
       <c r="C9" t="n">
-        <v>2.165</v>
+        <v>2.2993</v>
       </c>
       <c r="D9" t="n">
-        <v>1.0889</v>
+        <v>1.1379</v>
       </c>
       <c r="E9" t="n">
-        <v>3.7385</v>
+        <v>3.9705</v>
       </c>
       <c r="F9" t="n">
-        <v>3.486</v>
+        <v>3.9705</v>
       </c>
       <c r="G9" t="n">
-        <v>0.2525</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>3.486</v>
+        <v>3.9705</v>
       </c>
       <c r="I9" t="n">
-        <v>3.486</v>
+        <v>3.9705</v>
       </c>
       <c r="J9" t="n">
-        <v>0.2525</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>152</v>
+        <v>264</v>
       </c>
       <c r="L9" t="n">
-        <v>105</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>3.7385</v>
+        <v>3.9705</v>
       </c>
       <c r="N9" t="n">
-        <v>257</v>
+        <v>264</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ZywOo</t>
+          <t>stavn</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.652</v>
+        <v>3.7888</v>
       </c>
       <c r="C10" t="n">
-        <v>2.1149</v>
+        <v>2.1941</v>
       </c>
       <c r="D10" t="n">
-        <v>1.054</v>
+        <v>1.0655</v>
       </c>
       <c r="E10" t="n">
-        <v>3.652</v>
+        <v>3.7888</v>
       </c>
       <c r="F10" t="n">
-        <v>3.652</v>
+        <v>3.1468</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>0.642</v>
       </c>
       <c r="H10" t="n">
-        <v>3.652</v>
+        <v>3.1468</v>
       </c>
       <c r="I10" t="n">
-        <v>3.6689</v>
+        <v>3.1733</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>0.642</v>
       </c>
       <c r="K10" t="n">
-        <v>277</v>
+        <v>252</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="M10" t="n">
-        <v>3.6689</v>
+        <v>3.8153</v>
       </c>
       <c r="N10" t="n">
-        <v>277</v>
+        <v>332</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>m0NESY</t>
+          <t>ZywOo</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.2056</v>
+        <v>3.6383</v>
       </c>
       <c r="C11" t="n">
-        <v>1.8564</v>
+        <v>2.107</v>
       </c>
       <c r="D11" t="n">
-        <v>0.8736</v>
+        <v>1.0056</v>
       </c>
       <c r="E11" t="n">
-        <v>3.2056</v>
+        <v>3.6383</v>
       </c>
       <c r="F11" t="n">
-        <v>3.2056</v>
+        <v>3.6383</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>3.2056</v>
+        <v>3.6383</v>
       </c>
       <c r="I11" t="n">
-        <v>3.2056</v>
+        <v>3.6689</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>264</v>
+        <v>277</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>3.2056</v>
+        <v>3.6689</v>
       </c>
       <c r="N11" t="n">
-        <v>264</v>
+        <v>277</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>degster</t>
+          <t>Patsi</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3.1416</v>
+        <v>3.2215</v>
       </c>
       <c r="C12" t="n">
-        <v>1.8193</v>
+        <v>1.8656</v>
       </c>
       <c r="D12" t="n">
-        <v>0.8478</v>
+        <v>0.8395</v>
       </c>
       <c r="E12" t="n">
-        <v>3.1416</v>
+        <v>3.2215</v>
       </c>
       <c r="F12" t="n">
-        <v>1.3769</v>
+        <v>3.6057</v>
       </c>
       <c r="G12" t="n">
-        <v>1.7647</v>
+        <v>-0.3842</v>
       </c>
       <c r="H12" t="n">
-        <v>1.3769</v>
+        <v>3.6057</v>
       </c>
       <c r="I12" t="n">
-        <v>1.3769</v>
+        <v>3.6057</v>
       </c>
       <c r="J12" t="n">
-        <v>1.7647</v>
+        <v>-0.3842</v>
       </c>
       <c r="K12" t="n">
         <v>128</v>
@@ -989,7 +989,7 @@
         <v>129</v>
       </c>
       <c r="M12" t="n">
-        <v>3.1416</v>
+        <v>3.2215</v>
       </c>
       <c r="N12" t="n">
         <v>257</v>
@@ -998,185 +998,185 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>cadiaN</t>
+          <t>yuurih</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3.1128</v>
+        <v>3.155</v>
       </c>
       <c r="C13" t="n">
-        <v>1.8026</v>
+        <v>1.8271</v>
       </c>
       <c r="D13" t="n">
-        <v>0.8361</v>
+        <v>0.8129999999999999</v>
       </c>
       <c r="E13" t="n">
-        <v>3.1128</v>
+        <v>3.155</v>
       </c>
       <c r="F13" t="n">
-        <v>1.9126</v>
+        <v>3.2208</v>
       </c>
       <c r="G13" t="n">
-        <v>1.2002</v>
+        <v>-0.0658</v>
       </c>
       <c r="H13" t="n">
-        <v>1.9126</v>
+        <v>3.2208</v>
       </c>
       <c r="I13" t="n">
-        <v>1.9215</v>
+        <v>3.2208</v>
       </c>
       <c r="J13" t="n">
-        <v>1.2002</v>
+        <v>-0.0658</v>
       </c>
       <c r="K13" t="n">
-        <v>252</v>
+        <v>208</v>
       </c>
       <c r="L13" t="n">
-        <v>80</v>
+        <v>52</v>
       </c>
       <c r="M13" t="n">
-        <v>3.1217</v>
+        <v>3.155</v>
       </c>
       <c r="N13" t="n">
-        <v>332</v>
+        <v>260</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>fer</t>
+          <t>degster</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3.106</v>
+        <v>3.1416</v>
       </c>
       <c r="C14" t="n">
-        <v>1.7987</v>
+        <v>1.8193</v>
       </c>
       <c r="D14" t="n">
-        <v>0.8334</v>
+        <v>0.8077</v>
       </c>
       <c r="E14" t="n">
-        <v>3.106</v>
+        <v>3.1416</v>
       </c>
       <c r="F14" t="n">
-        <v>3.106</v>
+        <v>1.3769</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>1.7647</v>
       </c>
       <c r="H14" t="n">
-        <v>3.106</v>
+        <v>1.3769</v>
       </c>
       <c r="I14" t="n">
-        <v>3.106</v>
+        <v>1.3769</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>1.7647</v>
       </c>
       <c r="K14" t="n">
-        <v>264</v>
+        <v>128</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>129</v>
       </c>
       <c r="M14" t="n">
-        <v>3.106</v>
+        <v>3.1416</v>
       </c>
       <c r="N14" t="n">
-        <v>264</v>
+        <v>257</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>electroNic</t>
+          <t>cadiaN</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.9225</v>
+        <v>3.13</v>
       </c>
       <c r="C15" t="n">
-        <v>1.6924</v>
+        <v>1.8126</v>
       </c>
       <c r="D15" t="n">
-        <v>0.7593</v>
+        <v>0.8031</v>
       </c>
       <c r="E15" t="n">
-        <v>2.9225</v>
+        <v>3.13</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.08649999999999999</v>
+        <v>1.9298</v>
       </c>
       <c r="G15" t="n">
-        <v>3.009</v>
+        <v>1.2002</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.08649999999999999</v>
+        <v>1.9298</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.08649999999999999</v>
+        <v>1.946</v>
       </c>
       <c r="J15" t="n">
-        <v>3.009</v>
+        <v>1.2002</v>
       </c>
       <c r="K15" t="n">
-        <v>132</v>
+        <v>252</v>
       </c>
       <c r="L15" t="n">
-        <v>192</v>
+        <v>80</v>
       </c>
       <c r="M15" t="n">
-        <v>2.9225</v>
+        <v>3.1462</v>
       </c>
       <c r="N15" t="n">
-        <v>324</v>
+        <v>332</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Patsi</t>
+          <t>fer</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.8327</v>
+        <v>3.106</v>
       </c>
       <c r="C16" t="n">
-        <v>1.6404</v>
+        <v>1.7987</v>
       </c>
       <c r="D16" t="n">
-        <v>0.723</v>
+        <v>0.7935</v>
       </c>
       <c r="E16" t="n">
-        <v>2.8327</v>
+        <v>3.106</v>
       </c>
       <c r="F16" t="n">
-        <v>3.2169</v>
+        <v>3.106</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.3842</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>3.2169</v>
+        <v>3.106</v>
       </c>
       <c r="I16" t="n">
-        <v>3.2169</v>
+        <v>3.106</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.3842</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>128</v>
+        <v>264</v>
       </c>
       <c r="L16" t="n">
-        <v>129</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>2.8327</v>
+        <v>3.106</v>
       </c>
       <c r="N16" t="n">
-        <v>257</v>
+        <v>264</v>
       </c>
     </row>
     <row r="17">
@@ -1186,28 +1186,28 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2.7804</v>
+        <v>2.9943</v>
       </c>
       <c r="C17" t="n">
-        <v>1.6101</v>
+        <v>1.734</v>
       </c>
       <c r="D17" t="n">
-        <v>0.7019</v>
+        <v>0.749</v>
       </c>
       <c r="E17" t="n">
-        <v>2.7804</v>
+        <v>2.9943</v>
       </c>
       <c r="F17" t="n">
-        <v>2.6817</v>
+        <v>2.8956</v>
       </c>
       <c r="G17" t="n">
         <v>0.0987</v>
       </c>
       <c r="H17" t="n">
-        <v>2.6817</v>
+        <v>2.8956</v>
       </c>
       <c r="I17" t="n">
-        <v>2.6941</v>
+        <v>2.92</v>
       </c>
       <c r="J17" t="n">
         <v>0.0987</v>
@@ -1219,7 +1219,7 @@
         <v>79</v>
       </c>
       <c r="M17" t="n">
-        <v>2.7928</v>
+        <v>3.0187</v>
       </c>
       <c r="N17" t="n">
         <v>245</v>
@@ -1228,277 +1228,277 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>S1ren</t>
+          <t>electroNic</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2.6346</v>
+        <v>2.9225</v>
       </c>
       <c r="C18" t="n">
-        <v>1.5257</v>
+        <v>1.6924</v>
       </c>
       <c r="D18" t="n">
-        <v>0.643</v>
+        <v>0.7204</v>
       </c>
       <c r="E18" t="n">
-        <v>2.6346</v>
+        <v>2.9225</v>
       </c>
       <c r="F18" t="n">
-        <v>1.8258</v>
+        <v>-0.08649999999999999</v>
       </c>
       <c r="G18" t="n">
-        <v>0.8088</v>
+        <v>3.009</v>
       </c>
       <c r="H18" t="n">
-        <v>1.8258</v>
+        <v>-0.08649999999999999</v>
       </c>
       <c r="I18" t="n">
-        <v>1.8258</v>
+        <v>-0.08649999999999999</v>
       </c>
       <c r="J18" t="n">
-        <v>0.8088</v>
+        <v>3.009</v>
       </c>
       <c r="K18" t="n">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="L18" t="n">
-        <v>129</v>
+        <v>192</v>
       </c>
       <c r="M18" t="n">
-        <v>2.6346</v>
+        <v>2.9225</v>
       </c>
       <c r="N18" t="n">
-        <v>257</v>
+        <v>324</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>nicoodoz</t>
+          <t>S1ren</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2.4043</v>
+        <v>2.7461</v>
       </c>
       <c r="C19" t="n">
-        <v>1.3923</v>
+        <v>1.5903</v>
       </c>
       <c r="D19" t="n">
-        <v>0.5499000000000001</v>
+        <v>0.6501</v>
       </c>
       <c r="E19" t="n">
-        <v>2.4043</v>
+        <v>2.7461</v>
       </c>
       <c r="F19" t="n">
-        <v>2.7463</v>
+        <v>1.9373</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.342</v>
+        <v>0.8088</v>
       </c>
       <c r="H19" t="n">
-        <v>2.7463</v>
+        <v>1.9373</v>
       </c>
       <c r="I19" t="n">
-        <v>2.7719</v>
+        <v>1.9373</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.342</v>
+        <v>0.8088</v>
       </c>
       <c r="K19" t="n">
-        <v>264</v>
+        <v>128</v>
       </c>
       <c r="L19" t="n">
-        <v>54</v>
+        <v>129</v>
       </c>
       <c r="M19" t="n">
-        <v>2.4299</v>
+        <v>2.7461</v>
       </c>
       <c r="N19" t="n">
-        <v>318</v>
+        <v>257</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>yuurih</t>
+          <t>nicoodoz</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2.3411</v>
+        <v>2.526</v>
       </c>
       <c r="C20" t="n">
-        <v>1.3557</v>
+        <v>1.4628</v>
       </c>
       <c r="D20" t="n">
-        <v>0.5244</v>
+        <v>0.5624</v>
       </c>
       <c r="E20" t="n">
-        <v>2.3411</v>
+        <v>2.526</v>
       </c>
       <c r="F20" t="n">
-        <v>2.4069</v>
+        <v>2.868</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.0658</v>
+        <v>-0.342</v>
       </c>
       <c r="H20" t="n">
-        <v>2.4069</v>
+        <v>2.868</v>
       </c>
       <c r="I20" t="n">
-        <v>2.4069</v>
+        <v>2.9165</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.0658</v>
+        <v>-0.342</v>
       </c>
       <c r="K20" t="n">
-        <v>208</v>
+        <v>264</v>
       </c>
       <c r="L20" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="M20" t="n">
-        <v>2.3411</v>
+        <v>2.5745</v>
       </c>
       <c r="N20" t="n">
-        <v>260</v>
+        <v>318</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Perfecto</t>
+          <t>NiKo</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2.3155</v>
+        <v>2.3272</v>
       </c>
       <c r="C21" t="n">
-        <v>1.3409</v>
+        <v>1.3477</v>
       </c>
       <c r="D21" t="n">
-        <v>0.514</v>
+        <v>0.4832</v>
       </c>
       <c r="E21" t="n">
-        <v>2.3155</v>
+        <v>2.3272</v>
       </c>
       <c r="F21" t="n">
-        <v>1.7925</v>
+        <v>2.3272</v>
       </c>
       <c r="G21" t="n">
-        <v>0.523</v>
+        <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>1.7925</v>
+        <v>2.3272</v>
       </c>
       <c r="I21" t="n">
-        <v>1.7925</v>
+        <v>2.3272</v>
       </c>
       <c r="J21" t="n">
-        <v>0.523</v>
+        <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>132</v>
+        <v>264</v>
       </c>
       <c r="L21" t="n">
-        <v>192</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>2.3155</v>
+        <v>2.3272</v>
       </c>
       <c r="N21" t="n">
-        <v>324</v>
+        <v>264</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>NiKo</t>
+          <t>Perfecto</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2.2718</v>
+        <v>2.3155</v>
       </c>
       <c r="C22" t="n">
-        <v>1.3156</v>
+        <v>1.3409</v>
       </c>
       <c r="D22" t="n">
-        <v>0.4964</v>
+        <v>0.4786</v>
       </c>
       <c r="E22" t="n">
-        <v>2.2718</v>
+        <v>2.3155</v>
       </c>
       <c r="F22" t="n">
-        <v>2.2718</v>
+        <v>1.7925</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>0.523</v>
       </c>
       <c r="H22" t="n">
-        <v>2.2718</v>
+        <v>1.7925</v>
       </c>
       <c r="I22" t="n">
-        <v>2.2718</v>
+        <v>1.7925</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>0.523</v>
       </c>
       <c r="K22" t="n">
-        <v>264</v>
+        <v>132</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>192</v>
       </c>
       <c r="M22" t="n">
-        <v>2.2718</v>
+        <v>2.3155</v>
       </c>
       <c r="N22" t="n">
-        <v>264</v>
+        <v>324</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>KSCERATO</t>
+          <t>REZ</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1.907</v>
+        <v>2.2588</v>
       </c>
       <c r="C23" t="n">
-        <v>1.1044</v>
+        <v>1.3081</v>
       </c>
       <c r="D23" t="n">
-        <v>0.349</v>
+        <v>0.456</v>
       </c>
       <c r="E23" t="n">
-        <v>1.907</v>
+        <v>2.2588</v>
       </c>
       <c r="F23" t="n">
-        <v>2.907</v>
+        <v>2.3852</v>
       </c>
       <c r="G23" t="n">
-        <v>-1</v>
+        <v>-0.1264</v>
       </c>
       <c r="H23" t="n">
-        <v>2.907</v>
+        <v>2.3852</v>
       </c>
       <c r="I23" t="n">
-        <v>2.907</v>
+        <v>2.4053</v>
       </c>
       <c r="J23" t="n">
-        <v>-1</v>
+        <v>-0.1264</v>
       </c>
       <c r="K23" t="n">
-        <v>208</v>
+        <v>166</v>
       </c>
       <c r="L23" t="n">
-        <v>52</v>
+        <v>79</v>
       </c>
       <c r="M23" t="n">
-        <v>1.907</v>
+        <v>2.2789</v>
       </c>
       <c r="N23" t="n">
-        <v>260</v>
+        <v>245</v>
       </c>
     </row>
     <row r="24">
@@ -1508,28 +1508,28 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.8898</v>
+        <v>2.0181</v>
       </c>
       <c r="C24" t="n">
-        <v>1.0944</v>
+        <v>1.1687</v>
       </c>
       <c r="D24" t="n">
-        <v>0.3421</v>
+        <v>0.3601</v>
       </c>
       <c r="E24" t="n">
-        <v>1.8898</v>
+        <v>2.0181</v>
       </c>
       <c r="F24" t="n">
-        <v>1.8898</v>
+        <v>2.0181</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>1.8898</v>
+        <v>2.0181</v>
       </c>
       <c r="I24" t="n">
-        <v>1.8898</v>
+        <v>2.0181</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>1.8898</v>
+        <v>2.0181</v>
       </c>
       <c r="N24" t="n">
         <v>179</v>
@@ -1550,81 +1550,81 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>hampus</t>
+          <t>Zyphon</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1.8646</v>
+        <v>2.0137</v>
       </c>
       <c r="C25" t="n">
-        <v>1.0798</v>
+        <v>1.1661</v>
       </c>
       <c r="D25" t="n">
-        <v>0.3319</v>
+        <v>0.3583</v>
       </c>
       <c r="E25" t="n">
-        <v>1.8646</v>
+        <v>2.0137</v>
       </c>
       <c r="F25" t="n">
-        <v>1.16</v>
+        <v>1.6956</v>
       </c>
       <c r="G25" t="n">
-        <v>0.7046</v>
+        <v>0.3181</v>
       </c>
       <c r="H25" t="n">
-        <v>1.16</v>
+        <v>1.6956</v>
       </c>
       <c r="I25" t="n">
-        <v>1.1654</v>
+        <v>1.7242</v>
       </c>
       <c r="J25" t="n">
-        <v>0.7046</v>
+        <v>0.3181</v>
       </c>
       <c r="K25" t="n">
-        <v>166</v>
+        <v>264</v>
       </c>
       <c r="L25" t="n">
-        <v>79</v>
+        <v>54</v>
       </c>
       <c r="M25" t="n">
-        <v>1.87</v>
+        <v>2.0423</v>
       </c>
       <c r="N25" t="n">
-        <v>245</v>
+        <v>318</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>karrigan</t>
+          <t>Twistzz</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1.807</v>
+        <v>1.9721</v>
       </c>
       <c r="C26" t="n">
-        <v>1.0464</v>
+        <v>1.1421</v>
       </c>
       <c r="D26" t="n">
-        <v>0.3086</v>
+        <v>0.3418</v>
       </c>
       <c r="E26" t="n">
-        <v>1.807</v>
+        <v>1.9721</v>
       </c>
       <c r="F26" t="n">
-        <v>1.9645</v>
+        <v>1.5528</v>
       </c>
       <c r="G26" t="n">
-        <v>-0.1575</v>
+        <v>0.4193</v>
       </c>
       <c r="H26" t="n">
-        <v>1.9645</v>
+        <v>1.5528</v>
       </c>
       <c r="I26" t="n">
-        <v>1.9645</v>
+        <v>1.5528</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.1575</v>
+        <v>0.4193</v>
       </c>
       <c r="K26" t="n">
         <v>148</v>
@@ -1633,7 +1633,7 @@
         <v>217</v>
       </c>
       <c r="M26" t="n">
-        <v>1.807</v>
+        <v>1.9721</v>
       </c>
       <c r="N26" t="n">
         <v>365</v>
@@ -1642,231 +1642,231 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Zyphon</t>
+          <t>KSCERATO</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1.7205</v>
+        <v>1.907</v>
       </c>
       <c r="C27" t="n">
-        <v>0.9963</v>
+        <v>1.1044</v>
       </c>
       <c r="D27" t="n">
-        <v>0.2737</v>
+        <v>0.3158</v>
       </c>
       <c r="E27" t="n">
-        <v>1.7205</v>
+        <v>1.907</v>
       </c>
       <c r="F27" t="n">
-        <v>1.4024</v>
+        <v>2.907</v>
       </c>
       <c r="G27" t="n">
-        <v>0.3181</v>
+        <v>-1</v>
       </c>
       <c r="H27" t="n">
-        <v>1.4024</v>
+        <v>2.907</v>
       </c>
       <c r="I27" t="n">
-        <v>1.4155</v>
+        <v>2.907</v>
       </c>
       <c r="J27" t="n">
-        <v>0.3181</v>
+        <v>-1</v>
       </c>
       <c r="K27" t="n">
-        <v>264</v>
+        <v>208</v>
       </c>
       <c r="L27" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="M27" t="n">
-        <v>1.7336</v>
+        <v>1.907</v>
       </c>
       <c r="N27" t="n">
-        <v>318</v>
+        <v>260</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>syrsoN</t>
+          <t>karrigan</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1.7107</v>
+        <v>1.8973</v>
       </c>
       <c r="C28" t="n">
-        <v>0.9907</v>
+        <v>1.0987</v>
       </c>
       <c r="D28" t="n">
-        <v>0.2697</v>
+        <v>0.312</v>
       </c>
       <c r="E28" t="n">
-        <v>1.7107</v>
+        <v>1.8973</v>
       </c>
       <c r="F28" t="n">
-        <v>1.7107</v>
+        <v>2.0548</v>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>-0.1575</v>
       </c>
       <c r="H28" t="n">
-        <v>1.7107</v>
+        <v>2.0548</v>
       </c>
       <c r="I28" t="n">
-        <v>1.7107</v>
+        <v>2.0548</v>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
+        <v>-0.1575</v>
       </c>
       <c r="K28" t="n">
-        <v>179</v>
+        <v>148</v>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>217</v>
       </c>
       <c r="M28" t="n">
-        <v>1.7107</v>
+        <v>1.8973</v>
       </c>
       <c r="N28" t="n">
-        <v>179</v>
+        <v>365</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Ax1Le</t>
+          <t>hampus</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1.5197</v>
+        <v>1.8603</v>
       </c>
       <c r="C29" t="n">
-        <v>0.8801</v>
+        <v>1.0773</v>
       </c>
       <c r="D29" t="n">
-        <v>0.1926</v>
+        <v>0.2972</v>
       </c>
       <c r="E29" t="n">
-        <v>1.5197</v>
+        <v>1.8603</v>
       </c>
       <c r="F29" t="n">
-        <v>1.5197</v>
+        <v>1.1557</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>0.7046</v>
       </c>
       <c r="H29" t="n">
-        <v>1.5197</v>
+        <v>1.1557</v>
       </c>
       <c r="I29" t="n">
-        <v>1.5197</v>
+        <v>1.1654</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>0.7046</v>
       </c>
       <c r="K29" t="n">
-        <v>174</v>
+        <v>166</v>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="M29" t="n">
-        <v>1.5197</v>
+        <v>1.87</v>
       </c>
       <c r="N29" t="n">
-        <v>174</v>
+        <v>245</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Twistzz</t>
+          <t>Ax1Le</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1.4837</v>
+        <v>1.8249</v>
       </c>
       <c r="C30" t="n">
-        <v>0.8592</v>
+        <v>1.0568</v>
       </c>
       <c r="D30" t="n">
-        <v>0.178</v>
+        <v>0.2831</v>
       </c>
       <c r="E30" t="n">
-        <v>1.4837</v>
+        <v>1.8249</v>
       </c>
       <c r="F30" t="n">
-        <v>1.0644</v>
+        <v>1.8249</v>
       </c>
       <c r="G30" t="n">
-        <v>0.4193</v>
+        <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>1.0644</v>
+        <v>1.8249</v>
       </c>
       <c r="I30" t="n">
-        <v>1.0644</v>
+        <v>1.8249</v>
       </c>
       <c r="J30" t="n">
-        <v>0.4193</v>
+        <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>148</v>
+        <v>174</v>
       </c>
       <c r="L30" t="n">
-        <v>217</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>1.4837</v>
+        <v>1.8249</v>
       </c>
       <c r="N30" t="n">
-        <v>365</v>
+        <v>174</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>REZ</t>
+          <t>syrsoN</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1.3704</v>
+        <v>1.7188</v>
       </c>
       <c r="C31" t="n">
-        <v>0.7936</v>
+        <v>0.9954</v>
       </c>
       <c r="D31" t="n">
-        <v>0.1322</v>
+        <v>0.2409</v>
       </c>
       <c r="E31" t="n">
-        <v>1.3704</v>
+        <v>1.7188</v>
       </c>
       <c r="F31" t="n">
-        <v>1.4968</v>
+        <v>1.7188</v>
       </c>
       <c r="G31" t="n">
-        <v>-0.1264</v>
+        <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>1.4968</v>
+        <v>1.7188</v>
       </c>
       <c r="I31" t="n">
-        <v>1.5037</v>
+        <v>1.7188</v>
       </c>
       <c r="J31" t="n">
-        <v>-0.1264</v>
+        <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>166</v>
+        <v>179</v>
       </c>
       <c r="L31" t="n">
-        <v>79</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>1.3773</v>
+        <v>1.7188</v>
       </c>
       <c r="N31" t="n">
-        <v>245</v>
+        <v>179</v>
       </c>
     </row>
     <row r="32">
@@ -1882,7 +1882,7 @@
         <v>0.7814</v>
       </c>
       <c r="D32" t="n">
-        <v>0.1237</v>
+        <v>0.09370000000000001</v>
       </c>
       <c r="E32" t="n">
         <v>1.3493</v>
@@ -1922,28 +1922,28 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1.3002</v>
+        <v>1.2959</v>
       </c>
       <c r="C33" t="n">
-        <v>0.753</v>
+        <v>0.7504999999999999</v>
       </c>
       <c r="D33" t="n">
-        <v>0.1039</v>
+        <v>0.07240000000000001</v>
       </c>
       <c r="E33" t="n">
-        <v>1.3002</v>
+        <v>1.2959</v>
       </c>
       <c r="F33" t="n">
-        <v>1.6473</v>
+        <v>1.643</v>
       </c>
       <c r="G33" t="n">
         <v>-0.3471</v>
       </c>
       <c r="H33" t="n">
-        <v>1.6473</v>
+        <v>1.643</v>
       </c>
       <c r="I33" t="n">
-        <v>1.655</v>
+        <v>1.6568</v>
       </c>
       <c r="J33" t="n">
         <v>-0.3471</v>
@@ -1955,7 +1955,7 @@
         <v>80</v>
       </c>
       <c r="M33" t="n">
-        <v>1.3079</v>
+        <v>1.3097</v>
       </c>
       <c r="N33" t="n">
         <v>332</v>
@@ -1964,679 +1964,679 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>NAF</t>
+          <t>YEKINDAR</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>1.1962</v>
+        <v>1.2257</v>
       </c>
       <c r="C34" t="n">
-        <v>0.6927</v>
+        <v>0.7098</v>
       </c>
       <c r="D34" t="n">
-        <v>0.0619</v>
+        <v>0.0444</v>
       </c>
       <c r="E34" t="n">
-        <v>1.1962</v>
+        <v>1.2257</v>
       </c>
       <c r="F34" t="n">
-        <v>1.1962</v>
+        <v>1.2257</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>1.1962</v>
+        <v>1.2257</v>
       </c>
       <c r="I34" t="n">
-        <v>1.1962</v>
+        <v>1.2257</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>102</v>
+        <v>155</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>1.1962</v>
+        <v>1.2257</v>
       </c>
       <c r="N34" t="n">
-        <v>102</v>
+        <v>155</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>magixx</t>
+          <t>TeSeS</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>1.109</v>
+        <v>1.225</v>
       </c>
       <c r="C35" t="n">
-        <v>0.6422</v>
+        <v>0.7094</v>
       </c>
       <c r="D35" t="n">
-        <v>0.0266</v>
+        <v>0.0441</v>
       </c>
       <c r="E35" t="n">
-        <v>1.109</v>
+        <v>1.225</v>
       </c>
       <c r="F35" t="n">
-        <v>1.0693</v>
+        <v>1.561</v>
       </c>
       <c r="G35" t="n">
-        <v>0.0397</v>
+        <v>-0.336</v>
       </c>
       <c r="H35" t="n">
-        <v>1.0693</v>
+        <v>1.561</v>
       </c>
       <c r="I35" t="n">
-        <v>1.0693</v>
+        <v>1.5741</v>
       </c>
       <c r="J35" t="n">
-        <v>0.0397</v>
+        <v>-0.336</v>
       </c>
       <c r="K35" t="n">
-        <v>128</v>
+        <v>252</v>
       </c>
       <c r="L35" t="n">
-        <v>129</v>
+        <v>80</v>
       </c>
       <c r="M35" t="n">
-        <v>1.109</v>
+        <v>1.2381</v>
       </c>
       <c r="N35" t="n">
-        <v>257</v>
+        <v>332</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Magisk</t>
+          <t>roeJ</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>1.0862</v>
+        <v>1.2052</v>
       </c>
       <c r="C36" t="n">
-        <v>0.629</v>
+        <v>0.6979</v>
       </c>
       <c r="D36" t="n">
-        <v>0.0174</v>
+        <v>0.0362</v>
       </c>
       <c r="E36" t="n">
-        <v>1.0862</v>
+        <v>1.2052</v>
       </c>
       <c r="F36" t="n">
-        <v>1.0862</v>
+        <v>1.4711</v>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
+        <v>-0.2659</v>
       </c>
       <c r="H36" t="n">
-        <v>1.0862</v>
+        <v>1.4711</v>
       </c>
       <c r="I36" t="n">
-        <v>1.0913</v>
+        <v>1.496</v>
       </c>
       <c r="J36" t="n">
-        <v>0</v>
+        <v>-0.2659</v>
       </c>
       <c r="K36" t="n">
-        <v>277</v>
+        <v>264</v>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="M36" t="n">
-        <v>1.0913</v>
+        <v>1.2301</v>
       </c>
       <c r="N36" t="n">
-        <v>277</v>
+        <v>318</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>TeSeS</t>
+          <t>NAF</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.6471</v>
+        <v>1.1962</v>
       </c>
       <c r="C37" t="n">
-        <v>0.3747</v>
+        <v>0.6927</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.1599</v>
+        <v>0.0327</v>
       </c>
       <c r="E37" t="n">
-        <v>0.6471</v>
+        <v>1.1962</v>
       </c>
       <c r="F37" t="n">
-        <v>0.9831</v>
+        <v>1.1962</v>
       </c>
       <c r="G37" t="n">
-        <v>-0.336</v>
+        <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>0.9831</v>
+        <v>1.1962</v>
       </c>
       <c r="I37" t="n">
-        <v>0.9876</v>
+        <v>1.1962</v>
       </c>
       <c r="J37" t="n">
-        <v>-0.336</v>
+        <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>252</v>
+        <v>102</v>
       </c>
       <c r="L37" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>0.6516</v>
+        <v>1.1962</v>
       </c>
       <c r="N37" t="n">
-        <v>332</v>
+        <v>102</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Qikert</t>
+          <t>magixx</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.6012</v>
+        <v>1.109</v>
       </c>
       <c r="C38" t="n">
-        <v>0.3482</v>
+        <v>0.6422</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.1785</v>
+        <v>-0.0021</v>
       </c>
       <c r="E38" t="n">
-        <v>0.6012</v>
+        <v>1.109</v>
       </c>
       <c r="F38" t="n">
-        <v>0.6012</v>
+        <v>1.0693</v>
       </c>
       <c r="G38" t="n">
-        <v>0</v>
+        <v>0.0397</v>
       </c>
       <c r="H38" t="n">
-        <v>0.6012</v>
+        <v>1.0693</v>
       </c>
       <c r="I38" t="n">
-        <v>0.6012</v>
+        <v>1.0693</v>
       </c>
       <c r="J38" t="n">
-        <v>0</v>
+        <v>0.0397</v>
       </c>
       <c r="K38" t="n">
-        <v>155</v>
+        <v>128</v>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>129</v>
       </c>
       <c r="M38" t="n">
-        <v>0.6012</v>
+        <v>1.109</v>
       </c>
       <c r="N38" t="n">
-        <v>155</v>
+        <v>257</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>YEKINDAR</t>
+          <t>Magisk</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.5883</v>
+        <v>1.0822</v>
       </c>
       <c r="C39" t="n">
-        <v>0.3407</v>
+        <v>0.6267</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.1837</v>
+        <v>-0.0128</v>
       </c>
       <c r="E39" t="n">
-        <v>0.5883</v>
+        <v>1.0822</v>
       </c>
       <c r="F39" t="n">
-        <v>0.5883</v>
+        <v>1.0822</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>0.5883</v>
+        <v>1.0822</v>
       </c>
       <c r="I39" t="n">
-        <v>0.5883</v>
+        <v>1.0913</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>155</v>
+        <v>277</v>
       </c>
       <c r="L39" t="n">
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>0.5883</v>
+        <v>1.0913</v>
       </c>
       <c r="N39" t="n">
-        <v>155</v>
+        <v>277</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>jabbi</t>
+          <t>es3tag</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.5685</v>
+        <v>0.8963</v>
       </c>
       <c r="C40" t="n">
-        <v>0.3292</v>
+        <v>0.5191</v>
       </c>
       <c r="D40" t="n">
-        <v>-0.1917</v>
+        <v>-0.0868</v>
       </c>
       <c r="E40" t="n">
-        <v>0.5685</v>
+        <v>0.8963</v>
       </c>
       <c r="F40" t="n">
-        <v>0.3897</v>
+        <v>1.4862</v>
       </c>
       <c r="G40" t="n">
-        <v>0.1788</v>
+        <v>-0.5899</v>
       </c>
       <c r="H40" t="n">
-        <v>0.3897</v>
+        <v>1.4862</v>
       </c>
       <c r="I40" t="n">
-        <v>0.3933</v>
+        <v>1.4987</v>
       </c>
       <c r="J40" t="n">
-        <v>0.1788</v>
+        <v>-0.5899</v>
       </c>
       <c r="K40" t="n">
-        <v>264</v>
+        <v>166</v>
       </c>
       <c r="L40" t="n">
-        <v>54</v>
+        <v>79</v>
       </c>
       <c r="M40" t="n">
-        <v>0.5720999999999999</v>
+        <v>0.9087999999999999</v>
       </c>
       <c r="N40" t="n">
-        <v>318</v>
+        <v>245</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Maden</t>
+          <t>jabbi</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.5597</v>
+        <v>0.8364</v>
       </c>
       <c r="C41" t="n">
-        <v>0.3241</v>
+        <v>0.4844</v>
       </c>
       <c r="D41" t="n">
-        <v>-0.1953</v>
+        <v>-0.1107</v>
       </c>
       <c r="E41" t="n">
-        <v>0.5597</v>
+        <v>0.8364</v>
       </c>
       <c r="F41" t="n">
-        <v>1.0707</v>
+        <v>0.6576</v>
       </c>
       <c r="G41" t="n">
-        <v>-0.511</v>
+        <v>0.1788</v>
       </c>
       <c r="H41" t="n">
-        <v>1.0707</v>
+        <v>0.6576</v>
       </c>
       <c r="I41" t="n">
-        <v>1.0707</v>
+        <v>0.6687</v>
       </c>
       <c r="J41" t="n">
-        <v>-0.511</v>
+        <v>0.1788</v>
       </c>
       <c r="K41" t="n">
-        <v>152</v>
+        <v>264</v>
       </c>
       <c r="L41" t="n">
-        <v>105</v>
+        <v>54</v>
       </c>
       <c r="M41" t="n">
-        <v>0.5597</v>
+        <v>0.8474999999999999</v>
       </c>
       <c r="N41" t="n">
-        <v>257</v>
+        <v>318</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>rigoN</t>
+          <t>Maden</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.5507</v>
+        <v>0.7518</v>
       </c>
       <c r="C42" t="n">
-        <v>0.3189</v>
+        <v>0.4354</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.1989</v>
+        <v>-0.1444</v>
       </c>
       <c r="E42" t="n">
-        <v>0.5507</v>
+        <v>0.7518</v>
       </c>
       <c r="F42" t="n">
-        <v>0.5507</v>
+        <v>1.2628</v>
       </c>
       <c r="G42" t="n">
-        <v>0</v>
+        <v>-0.511</v>
       </c>
       <c r="H42" t="n">
-        <v>0.5507</v>
+        <v>1.2628</v>
       </c>
       <c r="I42" t="n">
-        <v>0.5507</v>
+        <v>1.2628</v>
       </c>
       <c r="J42" t="n">
-        <v>0</v>
+        <v>-0.511</v>
       </c>
       <c r="K42" t="n">
-        <v>109</v>
+        <v>152</v>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="M42" t="n">
-        <v>0.5507</v>
+        <v>0.7517999999999999</v>
       </c>
       <c r="N42" t="n">
-        <v>109</v>
+        <v>257</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>roeJ</t>
+          <t>Qikert</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.5187</v>
+        <v>0.6012</v>
       </c>
       <c r="C43" t="n">
-        <v>0.3004</v>
+        <v>0.3482</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.2118</v>
+        <v>-0.2044</v>
       </c>
       <c r="E43" t="n">
-        <v>0.5187</v>
+        <v>0.6012</v>
       </c>
       <c r="F43" t="n">
-        <v>0.7846</v>
+        <v>0.6012</v>
       </c>
       <c r="G43" t="n">
-        <v>-0.2659</v>
+        <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>0.7846</v>
+        <v>0.6012</v>
       </c>
       <c r="I43" t="n">
-        <v>0.7919</v>
+        <v>0.6012</v>
       </c>
       <c r="J43" t="n">
-        <v>-0.2659</v>
+        <v>0</v>
       </c>
       <c r="K43" t="n">
-        <v>264</v>
+        <v>155</v>
       </c>
       <c r="L43" t="n">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>0.526</v>
+        <v>0.6012</v>
       </c>
       <c r="N43" t="n">
-        <v>318</v>
+        <v>155</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>tabseN</t>
+          <t>rigoN</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.2444</v>
+        <v>0.5507</v>
       </c>
       <c r="C44" t="n">
-        <v>0.1415</v>
+        <v>0.3189</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.3226</v>
+        <v>-0.2245</v>
       </c>
       <c r="E44" t="n">
-        <v>0.2444</v>
+        <v>0.5507</v>
       </c>
       <c r="F44" t="n">
-        <v>0.2444</v>
+        <v>0.5507</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>0.2444</v>
+        <v>0.5507</v>
       </c>
       <c r="I44" t="n">
-        <v>0.2444</v>
+        <v>0.5507</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>179</v>
+        <v>109</v>
       </c>
       <c r="L44" t="n">
         <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>0.2444</v>
+        <v>0.5507</v>
       </c>
       <c r="N44" t="n">
-        <v>179</v>
+        <v>109</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>es3tag</t>
+          <t>tabseN</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.2431</v>
+        <v>0.2646</v>
       </c>
       <c r="C45" t="n">
-        <v>0.1408</v>
+        <v>0.1532</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.3232</v>
+        <v>-0.3385</v>
       </c>
       <c r="E45" t="n">
-        <v>0.2431</v>
+        <v>0.2646</v>
       </c>
       <c r="F45" t="n">
-        <v>0.833</v>
+        <v>0.2646</v>
       </c>
       <c r="G45" t="n">
-        <v>-0.5899</v>
+        <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>0.833</v>
+        <v>0.2646</v>
       </c>
       <c r="I45" t="n">
-        <v>0.8369</v>
+        <v>0.2646</v>
       </c>
       <c r="J45" t="n">
-        <v>-0.5899</v>
+        <v>0</v>
       </c>
       <c r="K45" t="n">
-        <v>166</v>
+        <v>179</v>
       </c>
       <c r="L45" t="n">
-        <v>79</v>
+        <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>0.247</v>
+        <v>0.2646</v>
       </c>
       <c r="N45" t="n">
-        <v>245</v>
+        <v>179</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>FalleN</t>
+          <t>saffee</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.2185</v>
+        <v>0.2345</v>
       </c>
       <c r="C46" t="n">
-        <v>0.1265</v>
+        <v>0.1358</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.3331</v>
+        <v>-0.3505</v>
       </c>
       <c r="E46" t="n">
-        <v>0.2185</v>
+        <v>0.2345</v>
       </c>
       <c r="F46" t="n">
-        <v>0.2185</v>
+        <v>0.1481</v>
       </c>
       <c r="G46" t="n">
-        <v>0</v>
+        <v>0.0864</v>
       </c>
       <c r="H46" t="n">
-        <v>0.2185</v>
+        <v>0.1481</v>
       </c>
       <c r="I46" t="n">
-        <v>0.2185</v>
+        <v>0.1481</v>
       </c>
       <c r="J46" t="n">
-        <v>0</v>
+        <v>0.0864</v>
       </c>
       <c r="K46" t="n">
-        <v>264</v>
+        <v>208</v>
       </c>
       <c r="L46" t="n">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="M46" t="n">
-        <v>0.2185</v>
+        <v>0.2345</v>
       </c>
       <c r="N46" t="n">
-        <v>264</v>
+        <v>260</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>sh1ro</t>
+          <t>FalleN</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.0562</v>
+        <v>0.2185</v>
       </c>
       <c r="C47" t="n">
-        <v>0.0325</v>
+        <v>0.1265</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.3987</v>
+        <v>-0.3569</v>
       </c>
       <c r="E47" t="n">
-        <v>0.0562</v>
+        <v>0.2185</v>
       </c>
       <c r="F47" t="n">
-        <v>0.0562</v>
+        <v>0.2185</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>0.0562</v>
+        <v>0.2185</v>
       </c>
       <c r="I47" t="n">
-        <v>0.0562</v>
+        <v>0.2185</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
       </c>
       <c r="K47" t="n">
-        <v>174</v>
+        <v>264</v>
       </c>
       <c r="L47" t="n">
         <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>0.0562</v>
+        <v>0.2185</v>
       </c>
       <c r="N47" t="n">
-        <v>174</v>
+        <v>264</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>hades</t>
+          <t>Snappi</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.0162</v>
+        <v>0.1692</v>
       </c>
       <c r="C48" t="n">
-        <v>0.0094</v>
+        <v>0.098</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.4148</v>
+        <v>-0.3765</v>
       </c>
       <c r="E48" t="n">
-        <v>0.0162</v>
+        <v>0.1692</v>
       </c>
       <c r="F48" t="n">
-        <v>-0.1924</v>
+        <v>0.0646</v>
       </c>
       <c r="G48" t="n">
-        <v>0.2086</v>
+        <v>0.1046</v>
       </c>
       <c r="H48" t="n">
-        <v>-0.1924</v>
+        <v>0.0646</v>
       </c>
       <c r="I48" t="n">
-        <v>-0.1924</v>
+        <v>0.0646</v>
       </c>
       <c r="J48" t="n">
-        <v>0.2086</v>
+        <v>0.1046</v>
       </c>
       <c r="K48" t="n">
         <v>152</v>
@@ -2645,7 +2645,7 @@
         <v>105</v>
       </c>
       <c r="M48" t="n">
-        <v>0.01620000000000002</v>
+        <v>0.1692</v>
       </c>
       <c r="N48" t="n">
         <v>257</v>
@@ -2654,185 +2654,185 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Snappi</t>
+          <t>sh1ro</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>-0.0999</v>
+        <v>0.0562</v>
       </c>
       <c r="C49" t="n">
-        <v>-0.0579</v>
+        <v>0.0325</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.4617</v>
+        <v>-0.4215</v>
       </c>
       <c r="E49" t="n">
-        <v>-0.0999</v>
+        <v>0.0562</v>
       </c>
       <c r="F49" t="n">
-        <v>-0.2045</v>
+        <v>0.0562</v>
       </c>
       <c r="G49" t="n">
-        <v>0.1046</v>
+        <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>-0.2045</v>
+        <v>0.0562</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.2045</v>
+        <v>0.0562</v>
       </c>
       <c r="J49" t="n">
-        <v>0.1046</v>
+        <v>0</v>
       </c>
       <c r="K49" t="n">
-        <v>152</v>
+        <v>174</v>
       </c>
       <c r="L49" t="n">
-        <v>105</v>
+        <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>-0.09989999999999999</v>
+        <v>0.0562</v>
       </c>
       <c r="N49" t="n">
-        <v>257</v>
+        <v>174</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>boltz</t>
+          <t>hades</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>-0.1272</v>
+        <v>0.0253</v>
       </c>
       <c r="C50" t="n">
-        <v>-0.0737</v>
+        <v>0.0147</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.4727</v>
+        <v>-0.4338</v>
       </c>
       <c r="E50" t="n">
-        <v>-0.1272</v>
+        <v>0.0253</v>
       </c>
       <c r="F50" t="n">
-        <v>-0.1272</v>
+        <v>-0.1833</v>
       </c>
       <c r="G50" t="n">
-        <v>0</v>
+        <v>0.2086</v>
       </c>
       <c r="H50" t="n">
-        <v>-0.1272</v>
+        <v>-0.1833</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.1272</v>
+        <v>-0.1833</v>
       </c>
       <c r="J50" t="n">
-        <v>0</v>
+        <v>0.2086</v>
       </c>
       <c r="K50" t="n">
-        <v>264</v>
+        <v>152</v>
       </c>
       <c r="L50" t="n">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="M50" t="n">
-        <v>-0.1272</v>
+        <v>0.02530000000000002</v>
       </c>
       <c r="N50" t="n">
-        <v>264</v>
+        <v>257</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>dupreeh</t>
+          <t>boltz</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>-0.1334</v>
+        <v>-0.1272</v>
       </c>
       <c r="C51" t="n">
-        <v>-0.07729999999999999</v>
+        <v>-0.0737</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.4753</v>
+        <v>-0.4946</v>
       </c>
       <c r="E51" t="n">
-        <v>-0.1334</v>
+        <v>-0.1272</v>
       </c>
       <c r="F51" t="n">
-        <v>-0.1334</v>
+        <v>-0.1272</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>-0.1334</v>
+        <v>-0.1272</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.134</v>
+        <v>-0.1272</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
       </c>
       <c r="K51" t="n">
-        <v>277</v>
+        <v>264</v>
       </c>
       <c r="L51" t="n">
         <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>-0.134</v>
+        <v>-0.1272</v>
       </c>
       <c r="N51" t="n">
-        <v>277</v>
+        <v>264</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>buster</t>
+          <t>dupreeh</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>-0.2672</v>
+        <v>-0.1329</v>
       </c>
       <c r="C52" t="n">
-        <v>-0.1547</v>
+        <v>-0.077</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.5293</v>
+        <v>-0.4969</v>
       </c>
       <c r="E52" t="n">
-        <v>-0.2672</v>
+        <v>-0.1329</v>
       </c>
       <c r="F52" t="n">
-        <v>-0.2672</v>
+        <v>-0.1329</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
       </c>
       <c r="H52" t="n">
-        <v>-0.2672</v>
+        <v>-0.1329</v>
       </c>
       <c r="I52" t="n">
-        <v>-0.2672</v>
+        <v>-0.134</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
       </c>
       <c r="K52" t="n">
-        <v>155</v>
+        <v>277</v>
       </c>
       <c r="L52" t="n">
         <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>-0.2672</v>
+        <v>-0.134</v>
       </c>
       <c r="N52" t="n">
-        <v>155</v>
+        <v>277</v>
       </c>
     </row>
     <row r="53">
@@ -2842,28 +2842,28 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>-0.3303</v>
+        <v>-0.2358</v>
       </c>
       <c r="C53" t="n">
-        <v>-0.1913</v>
+        <v>-0.1366</v>
       </c>
       <c r="D53" t="n">
-        <v>-0.5548</v>
+        <v>-0.5379</v>
       </c>
       <c r="E53" t="n">
-        <v>-0.3303</v>
+        <v>-0.2358</v>
       </c>
       <c r="F53" t="n">
-        <v>-1.3405</v>
+        <v>-1.246</v>
       </c>
       <c r="G53" t="n">
         <v>1.0102</v>
       </c>
       <c r="H53" t="n">
-        <v>-1.3405</v>
+        <v>-1.246</v>
       </c>
       <c r="I53" t="n">
-        <v>-1.3405</v>
+        <v>-1.246</v>
       </c>
       <c r="J53" t="n">
         <v>1.0102</v>
@@ -2875,7 +2875,7 @@
         <v>192</v>
       </c>
       <c r="M53" t="n">
-        <v>-0.3303</v>
+        <v>-0.2358</v>
       </c>
       <c r="N53" t="n">
         <v>324</v>
@@ -2884,32 +2884,32 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Jame</t>
+          <t>buster</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>-0.351</v>
+        <v>-0.2672</v>
       </c>
       <c r="C54" t="n">
-        <v>-0.2033</v>
+        <v>-0.1547</v>
       </c>
       <c r="D54" t="n">
-        <v>-0.5632</v>
+        <v>-0.5504</v>
       </c>
       <c r="E54" t="n">
-        <v>-0.351</v>
+        <v>-0.2672</v>
       </c>
       <c r="F54" t="n">
-        <v>-0.351</v>
+        <v>-0.2672</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
       </c>
       <c r="H54" t="n">
-        <v>-0.351</v>
+        <v>-0.2672</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.351</v>
+        <v>-0.2672</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -2921,7 +2921,7 @@
         <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>-0.351</v>
+        <v>-0.2672</v>
       </c>
       <c r="N54" t="n">
         <v>155</v>
@@ -2934,28 +2934,28 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>-0.3588</v>
+        <v>-0.288</v>
       </c>
       <c r="C55" t="n">
-        <v>-0.2078</v>
+        <v>-0.1668</v>
       </c>
       <c r="D55" t="n">
-        <v>-0.5663</v>
+        <v>-0.5586</v>
       </c>
       <c r="E55" t="n">
-        <v>-0.3588</v>
+        <v>-0.288</v>
       </c>
       <c r="F55" t="n">
-        <v>-0.3588</v>
+        <v>-0.288</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
       </c>
       <c r="H55" t="n">
-        <v>-0.3588</v>
+        <v>-0.288</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.3588</v>
+        <v>-0.288</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -2967,7 +2967,7 @@
         <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>-0.3588</v>
+        <v>-0.288</v>
       </c>
       <c r="N55" t="n">
         <v>174</v>
@@ -2976,415 +2976,415 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>saffee</t>
+          <t>Jame</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>-0.3746</v>
+        <v>-0.351</v>
       </c>
       <c r="C56" t="n">
-        <v>-0.2169</v>
+        <v>-0.2033</v>
       </c>
       <c r="D56" t="n">
-        <v>-0.5727</v>
+        <v>-0.5837</v>
       </c>
       <c r="E56" t="n">
-        <v>-0.3746</v>
+        <v>-0.351</v>
       </c>
       <c r="F56" t="n">
-        <v>-0.461</v>
+        <v>-0.351</v>
       </c>
       <c r="G56" t="n">
-        <v>0.0864</v>
+        <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>-0.461</v>
+        <v>-0.351</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.461</v>
+        <v>-0.351</v>
       </c>
       <c r="J56" t="n">
-        <v>0.0864</v>
+        <v>0</v>
       </c>
       <c r="K56" t="n">
-        <v>208</v>
+        <v>155</v>
       </c>
       <c r="L56" t="n">
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>-0.3746</v>
+        <v>-0.351</v>
       </c>
       <c r="N56" t="n">
-        <v>260</v>
+        <v>155</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Plopski</t>
+          <t>FL1T</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>-0.4438</v>
+        <v>-0.3793</v>
       </c>
       <c r="C57" t="n">
-        <v>-0.257</v>
+        <v>-0.2197</v>
       </c>
       <c r="D57" t="n">
-        <v>-0.6006</v>
+        <v>-0.595</v>
       </c>
       <c r="E57" t="n">
-        <v>-0.4438</v>
+        <v>-0.3793</v>
       </c>
       <c r="F57" t="n">
-        <v>0.4209</v>
+        <v>-0.3793</v>
       </c>
       <c r="G57" t="n">
-        <v>-0.8647</v>
+        <v>0</v>
       </c>
       <c r="H57" t="n">
-        <v>0.4209</v>
+        <v>-0.3793</v>
       </c>
       <c r="I57" t="n">
-        <v>0.4229</v>
+        <v>-0.3793</v>
       </c>
       <c r="J57" t="n">
-        <v>-0.8647</v>
+        <v>0</v>
       </c>
       <c r="K57" t="n">
-        <v>166</v>
+        <v>155</v>
       </c>
       <c r="L57" t="n">
-        <v>79</v>
+        <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>-0.4418</v>
+        <v>-0.3793</v>
       </c>
       <c r="N57" t="n">
-        <v>245</v>
+        <v>155</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>juanflatroo</t>
+          <t>Plopski</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>-0.4984</v>
+        <v>-0.4454</v>
       </c>
       <c r="C58" t="n">
-        <v>-0.2886</v>
+        <v>-0.2579</v>
       </c>
       <c r="D58" t="n">
-        <v>-0.6227</v>
+        <v>-0.6214</v>
       </c>
       <c r="E58" t="n">
-        <v>-0.4984</v>
+        <v>-0.4454</v>
       </c>
       <c r="F58" t="n">
-        <v>-0.4984</v>
+        <v>0.4193</v>
       </c>
       <c r="G58" t="n">
-        <v>0</v>
+        <v>-0.8647</v>
       </c>
       <c r="H58" t="n">
-        <v>-0.4984</v>
+        <v>0.4193</v>
       </c>
       <c r="I58" t="n">
-        <v>-0.4984</v>
+        <v>0.4229</v>
       </c>
       <c r="J58" t="n">
-        <v>0</v>
+        <v>-0.8647</v>
       </c>
       <c r="K58" t="n">
-        <v>109</v>
+        <v>166</v>
       </c>
       <c r="L58" t="n">
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="M58" t="n">
-        <v>-0.4984</v>
+        <v>-0.4418</v>
       </c>
       <c r="N58" t="n">
-        <v>109</v>
+        <v>245</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>nafany</t>
+          <t>juanflatroo</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>-0.5439000000000001</v>
+        <v>-0.4984</v>
       </c>
       <c r="C59" t="n">
-        <v>-0.315</v>
+        <v>-0.2886</v>
       </c>
       <c r="D59" t="n">
-        <v>-0.6411</v>
+        <v>-0.6425</v>
       </c>
       <c r="E59" t="n">
-        <v>-0.5439000000000001</v>
+        <v>-0.4984</v>
       </c>
       <c r="F59" t="n">
-        <v>-0.5439000000000001</v>
+        <v>-0.4984</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
       </c>
       <c r="H59" t="n">
-        <v>-0.5439000000000001</v>
+        <v>-0.4984</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.5439000000000001</v>
+        <v>-0.4984</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
       </c>
       <c r="K59" t="n">
-        <v>174</v>
+        <v>109</v>
       </c>
       <c r="L59" t="n">
         <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>-0.5439000000000001</v>
+        <v>-0.4984</v>
       </c>
       <c r="N59" t="n">
-        <v>174</v>
+        <v>109</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>apEX</t>
+          <t>nafany</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>-0.6128</v>
+        <v>-0.5439000000000001</v>
       </c>
       <c r="C60" t="n">
-        <v>-0.3549</v>
+        <v>-0.315</v>
       </c>
       <c r="D60" t="n">
-        <v>-0.6689000000000001</v>
+        <v>-0.6606</v>
       </c>
       <c r="E60" t="n">
-        <v>-0.6128</v>
+        <v>-0.5439000000000001</v>
       </c>
       <c r="F60" t="n">
-        <v>-0.6128</v>
+        <v>-0.5439000000000001</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
       </c>
       <c r="H60" t="n">
-        <v>-0.6128</v>
+        <v>-0.5439000000000001</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.6156</v>
+        <v>-0.5439000000000001</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
       </c>
       <c r="K60" t="n">
-        <v>277</v>
+        <v>174</v>
       </c>
       <c r="L60" t="n">
         <v>0</v>
       </c>
       <c r="M60" t="n">
-        <v>-0.6156</v>
+        <v>-0.5439000000000001</v>
       </c>
       <c r="N60" t="n">
-        <v>277</v>
+        <v>174</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>nitr0</t>
+          <t>apEX</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>-0.7148</v>
+        <v>-0.6105</v>
       </c>
       <c r="C61" t="n">
-        <v>-0.4139</v>
+        <v>-0.3535</v>
       </c>
       <c r="D61" t="n">
-        <v>-0.7101</v>
+        <v>-0.6871</v>
       </c>
       <c r="E61" t="n">
-        <v>-0.7148</v>
+        <v>-0.6105</v>
       </c>
       <c r="F61" t="n">
-        <v>-0.7148</v>
+        <v>-0.6105</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
       </c>
       <c r="H61" t="n">
-        <v>-0.7148</v>
+        <v>-0.6105</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.7148</v>
+        <v>-0.6156</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
       </c>
       <c r="K61" t="n">
-        <v>102</v>
+        <v>277</v>
       </c>
       <c r="L61" t="n">
         <v>0</v>
       </c>
       <c r="M61" t="n">
-        <v>-0.7148</v>
+        <v>-0.6156</v>
       </c>
       <c r="N61" t="n">
-        <v>102</v>
+        <v>277</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>HObbit</t>
+          <t>nitr0</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>-0.7184</v>
+        <v>-0.7148</v>
       </c>
       <c r="C62" t="n">
-        <v>-0.416</v>
+        <v>-0.4139</v>
       </c>
       <c r="D62" t="n">
-        <v>-0.7116</v>
+        <v>-0.7287</v>
       </c>
       <c r="E62" t="n">
-        <v>-0.7184</v>
+        <v>-0.7148</v>
       </c>
       <c r="F62" t="n">
-        <v>-0.7184</v>
+        <v>-0.7148</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
       </c>
       <c r="H62" t="n">
-        <v>-0.7184</v>
+        <v>-0.7148</v>
       </c>
       <c r="I62" t="n">
-        <v>-0.7184</v>
+        <v>-0.7148</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
       </c>
       <c r="K62" t="n">
-        <v>174</v>
+        <v>102</v>
       </c>
       <c r="L62" t="n">
         <v>0</v>
       </c>
       <c r="M62" t="n">
-        <v>-0.7184</v>
+        <v>-0.7148</v>
       </c>
       <c r="N62" t="n">
-        <v>174</v>
+        <v>102</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>oSee</t>
+          <t>HObbit</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>-0.7362</v>
+        <v>-0.7184</v>
       </c>
       <c r="C63" t="n">
-        <v>-0.4263</v>
+        <v>-0.416</v>
       </c>
       <c r="D63" t="n">
-        <v>-0.7188</v>
+        <v>-0.7301</v>
       </c>
       <c r="E63" t="n">
-        <v>-0.7362</v>
+        <v>-0.7184</v>
       </c>
       <c r="F63" t="n">
-        <v>-0.7362</v>
+        <v>-0.7184</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
       </c>
       <c r="H63" t="n">
-        <v>-0.7362</v>
+        <v>-0.7184</v>
       </c>
       <c r="I63" t="n">
-        <v>-0.7362</v>
+        <v>-0.7184</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
       </c>
       <c r="K63" t="n">
-        <v>102</v>
+        <v>174</v>
       </c>
       <c r="L63" t="n">
         <v>0</v>
       </c>
       <c r="M63" t="n">
-        <v>-0.7362</v>
+        <v>-0.7184</v>
       </c>
       <c r="N63" t="n">
-        <v>102</v>
+        <v>174</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>FL1T</t>
+          <t>oSee</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>-0.7367</v>
+        <v>-0.7362</v>
       </c>
       <c r="C64" t="n">
-        <v>-0.4266</v>
+        <v>-0.4263</v>
       </c>
       <c r="D64" t="n">
-        <v>-0.719</v>
+        <v>-0.7372</v>
       </c>
       <c r="E64" t="n">
-        <v>-0.7367</v>
+        <v>-0.7362</v>
       </c>
       <c r="F64" t="n">
-        <v>-0.7367</v>
+        <v>-0.7362</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
       </c>
       <c r="H64" t="n">
-        <v>-0.7367</v>
+        <v>-0.7362</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.7367</v>
+        <v>-0.7362</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
       </c>
       <c r="K64" t="n">
-        <v>155</v>
+        <v>102</v>
       </c>
       <c r="L64" t="n">
         <v>0</v>
       </c>
       <c r="M64" t="n">
-        <v>-0.7367</v>
+        <v>-0.7362</v>
       </c>
       <c r="N64" t="n">
-        <v>155</v>
+        <v>102</v>
       </c>
     </row>
     <row r="65">
@@ -3400,7 +3400,7 @@
         <v>-0.4569</v>
       </c>
       <c r="D65" t="n">
-        <v>-0.7401</v>
+        <v>-0.7582</v>
       </c>
       <c r="E65" t="n">
         <v>-0.7889</v>
@@ -3446,7 +3446,7 @@
         <v>-0.4899</v>
       </c>
       <c r="D66" t="n">
-        <v>-0.7631</v>
+        <v>-0.7809</v>
       </c>
       <c r="E66" t="n">
         <v>-0.8459</v>
@@ -3486,25 +3486,25 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>-0.8732</v>
+        <v>-0.87</v>
       </c>
       <c r="C67" t="n">
-        <v>-0.5057</v>
+        <v>-0.5038</v>
       </c>
       <c r="D67" t="n">
-        <v>-0.7741</v>
+        <v>-0.7905</v>
       </c>
       <c r="E67" t="n">
-        <v>-0.8732</v>
+        <v>-0.87</v>
       </c>
       <c r="F67" t="n">
-        <v>-0.8732</v>
+        <v>-0.87</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
       </c>
       <c r="H67" t="n">
-        <v>-0.8732</v>
+        <v>-0.87</v>
       </c>
       <c r="I67" t="n">
         <v>-0.8773</v>
@@ -3538,7 +3538,7 @@
         <v>-0.5301</v>
       </c>
       <c r="D68" t="n">
-        <v>-0.7911</v>
+        <v>-0.8086</v>
       </c>
       <c r="E68" t="n">
         <v>-0.9153</v>
@@ -3584,7 +3584,7 @@
         <v>-0.5737</v>
       </c>
       <c r="D69" t="n">
-        <v>-0.8215</v>
+        <v>-0.8386</v>
       </c>
       <c r="E69" t="n">
         <v>-0.9906</v>
@@ -3630,7 +3630,7 @@
         <v>-0.7407</v>
       </c>
       <c r="D70" t="n">
-        <v>-0.9381</v>
+        <v>-0.9535</v>
       </c>
       <c r="E70" t="n">
         <v>-1.2791</v>
@@ -3676,7 +3676,7 @@
         <v>-0.8256</v>
       </c>
       <c r="D71" t="n">
-        <v>-0.9973</v>
+        <v>-1.0119</v>
       </c>
       <c r="E71" t="n">
         <v>-1.4256</v>
@@ -3722,7 +3722,7 @@
         <v>-0.8421999999999999</v>
       </c>
       <c r="D72" t="n">
-        <v>-1.0089</v>
+        <v>-1.0233</v>
       </c>
       <c r="E72" t="n">
         <v>-1.4544</v>
@@ -3768,7 +3768,7 @@
         <v>-0.8743</v>
       </c>
       <c r="D73" t="n">
-        <v>-1.0313</v>
+        <v>-1.0454</v>
       </c>
       <c r="E73" t="n">
         <v>-1.5098</v>
@@ -3814,7 +3814,7 @@
         <v>-1.0972</v>
       </c>
       <c r="D74" t="n">
-        <v>-1.1867</v>
+        <v>-1.1987</v>
       </c>
       <c r="E74" t="n">
         <v>-1.8946</v>
@@ -3860,7 +3860,7 @@
         <v>-1.1076</v>
       </c>
       <c r="D75" t="n">
-        <v>-1.194</v>
+        <v>-1.2059</v>
       </c>
       <c r="E75" t="n">
         <v>-1.9126</v>
@@ -3906,7 +3906,7 @@
         <v>-1.2139</v>
       </c>
       <c r="D76" t="n">
-        <v>-1.2681</v>
+        <v>-1.279</v>
       </c>
       <c r="E76" t="n">
         <v>-2.0961</v>
@@ -3952,7 +3952,7 @@
         <v>-1.3791</v>
       </c>
       <c r="D77" t="n">
-        <v>-1.3834</v>
+        <v>-1.3927</v>
       </c>
       <c r="E77" t="n">
         <v>-2.3815</v>
@@ -3998,7 +3998,7 @@
         <v>-1.597</v>
       </c>
       <c r="D78" t="n">
-        <v>-1.5354</v>
+        <v>-1.5426</v>
       </c>
       <c r="E78" t="n">
         <v>-2.7577</v>
@@ -4044,7 +4044,7 @@
         <v>-1.7532</v>
       </c>
       <c r="D79" t="n">
-        <v>-1.6444</v>
+        <v>-1.6501</v>
       </c>
       <c r="E79" t="n">
         <v>-3.0275</v>
@@ -4084,25 +4084,25 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>-3.2611</v>
+        <v>-3.2526</v>
       </c>
       <c r="C80" t="n">
-        <v>-1.8885</v>
+        <v>-1.8836</v>
       </c>
       <c r="D80" t="n">
-        <v>-1.7388</v>
+        <v>-1.7397</v>
       </c>
       <c r="E80" t="n">
-        <v>-3.2611</v>
+        <v>-3.2526</v>
       </c>
       <c r="F80" t="n">
-        <v>-2.2611</v>
+        <v>-2.2526</v>
       </c>
       <c r="G80" t="n">
         <v>-1</v>
       </c>
       <c r="H80" t="n">
-        <v>-2.2611</v>
+        <v>-2.2526</v>
       </c>
       <c r="I80" t="n">
         <v>-2.2716</v>
@@ -4130,25 +4130,25 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>-3.91</v>
+        <v>-3.8884</v>
       </c>
       <c r="C81" t="n">
-        <v>-2.2643</v>
+        <v>-2.2518</v>
       </c>
       <c r="D81" t="n">
-        <v>-2.0009</v>
+        <v>-1.993</v>
       </c>
       <c r="E81" t="n">
-        <v>-3.91</v>
+        <v>-3.8884</v>
       </c>
       <c r="F81" t="n">
-        <v>-2.91</v>
+        <v>-2.8884</v>
       </c>
       <c r="G81" t="n">
         <v>-1</v>
       </c>
       <c r="H81" t="n">
-        <v>-2.91</v>
+        <v>-2.8884</v>
       </c>
       <c r="I81" t="n">
         <v>-2.9372</v>
